--- a/Downloads/Splitflask-Financials/deliverables/SGM_2025_Amendment_Packet.xlsx
+++ b/Downloads/Splitflask-Financials/deliverables/SGM_2025_Amendment_Packet.xlsx
@@ -143,7 +143,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -165,11 +165,55 @@
         <color rgb="00AAAAAA"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -279,6 +323,8 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -644,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -811,11 +857,11 @@
       </c>
       <c r="B12" s="12" t="n"/>
       <c r="C12" s="13" t="n">
-        <v>74511</v>
+        <v>67398.78999999999</v>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Amazon fee $7,071 + Augusta rent $16,500 + FB ads $16,340 + bank-classified opex $34,600. See tab 5. Provisional pending TJ itemization of $34,600 block.</t>
+          <t>Itemized from SGM_2025_Txns — FINAL subject to TJ calls</t>
         </is>
       </c>
     </row>
@@ -829,11 +875,11 @@
         <v>-32900</v>
       </c>
       <c r="C13" s="18" t="n">
-        <v>-19027</v>
+        <v>-11915</v>
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>Loss deepens vs as-filed. Amendment does NOT raise tax. Cures $240K 1099-K matching exposure.</t>
+          <t>Favorable; does NOT raise tax — shallower than provisional −$19,027</t>
         </is>
       </c>
     </row>
@@ -850,6 +896,9 @@
           <t xml:space="preserve">  1. DEPOSIT-BASIS ERROR — CORRECTED:  Filed return used total bank deposits ($130,976) as gross receipts. Deposits included $57,317 owner loans + $11,151 interco transfers = $68,468 of non-income, inflating filed gross by that amount. Additionally, a $7,024 reclassification (reversals/misc) was removed in Layer 12. Amendment restates on real-revenue basis: $55,484.</t>
         </is>
       </c>
+      <c r="B16" s="37" t="n"/>
+      <c r="C16" s="37" t="n"/>
+      <c r="D16" s="38" t="n"/>
     </row>
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="22" t="inlineStr">
@@ -857,6 +906,9 @@
           <t xml:space="preserve">  2. AMAZON 1099-K NOMINEE MECHANICS (CENTERPIECE):  Amazon 1099-K $240,009.89 issued on SGM TIN because TIN update lagged when the account physically moved to SPLT (formed Jan 28, 2025). Resolution: SGM reports full $240,009.89 IN, deducts $224,789.09 OUT as Nominee Distribution, issues nominee 1099 to SPLT. SGM nets $15,220.80 (Jan 1–Feb 4 earned orders). TJ: also request corrected 1099-K from Amazon under SPLT TIN (belt-and-suspenders).</t>
         </is>
       </c>
+      <c r="B17" s="37" t="n"/>
+      <c r="C17" s="37" t="n"/>
+      <c r="D17" s="38" t="n"/>
     </row>
     <row r="18" ht="60" customHeight="1">
       <c r="A18" s="21" t="inlineStr">
@@ -864,6 +916,9 @@
           <t xml:space="preserve">  3. FILED DEDUCTION DETAIL — TJ TO VERIFY (CB 2024 LESSON):  Filed gross $130,976 − filed net −$32,900 = implied filed expenses $163,876. Filed deduction schedule NOT available in source docs. TJ to provide filed 1120-S for deduction-by-deduction comparison. CB 2024 found $104K of unsubstantiated QuickBooks catch-all deductions — apply same scrutiny here.</t>
         </is>
       </c>
+      <c r="B18" s="37" t="n"/>
+      <c r="C18" s="37" t="n"/>
+      <c r="D18" s="38" t="n"/>
     </row>
     <row r="19" ht="60" customHeight="1">
       <c r="A19" s="22" t="inlineStr">
@@ -871,11 +926,24 @@
           <t xml:space="preserve">  4. $148K SGM→SPLT TRANSFER — TJ LOAN-VS-CAPITAL DECISION:  $148,164 operating cash moved from SGM to SPLT as business shifted entities mid-2025. NOT P&amp;L. TJ: LOAN = interco receivable(SGM)/payable(SPLT); CAPITAL = permanent equity. $148K is material.</t>
         </is>
       </c>
+      <c r="B19" s="37" t="n"/>
+      <c r="C19" s="37" t="n"/>
+      <c r="D19" s="38" t="n"/>
     </row>
     <row r="20" ht="60" customHeight="1">
       <c r="A20" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. AUGUSTA RENT $16,500 — PENDING TJ CONFIRMATION:  Bank-substantiated. Deductibility requires: (a) 14-day annual cap not exceeded, (b) no home-office double-stack. TJ confirms and approves inclusion.</t>
+        </is>
+      </c>
+      <c r="B20" s="37" t="n"/>
+      <c r="C20" s="37" t="n"/>
+      <c r="D20" s="38" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Note: $34,600 provisional opex block replaced by $27,487.79 bank-itemized opex. Drop of $7,112 (block was over-stated). TJ adjustments (vehicle insurance $820, meals 50%, personal items ~$601, travel docs) could further reduce loss by $0–$1,421.</t>
         </is>
       </c>
     </row>
@@ -1029,6 +1097,10 @@
           <t>STEP 1: SGM reports the FULL $240,009.89 Amazon 1099-K on its 2025 1120-S income (Line 1). IRS matching satisfied at SGM TIN.</t>
         </is>
       </c>
+      <c r="B10" s="37" t="n"/>
+      <c r="C10" s="37" t="n"/>
+      <c r="D10" s="37" t="n"/>
+      <c r="E10" s="38" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="22" t="inlineStr">
@@ -1036,6 +1108,10 @@
           <t>STEP 2: SGM deducts $224,789.09 as Nominee Distribution (Other Deductions line, labeled 'Nominee Distribution to SPLT INC EIN 33-3094308').</t>
         </is>
       </c>
+      <c r="B11" s="37" t="n"/>
+      <c r="C11" s="37" t="n"/>
+      <c r="D11" s="37" t="n"/>
+      <c r="E11" s="38" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="21" t="inlineStr">
@@ -1043,6 +1119,10 @@
           <t>STEP 3: SGM issues Form 1099 (nominee) to SPLT INC (EIN 33-3094308) for $224,789.09. TJ files this form.</t>
         </is>
       </c>
+      <c r="B12" s="37" t="n"/>
+      <c r="C12" s="37" t="n"/>
+      <c r="D12" s="37" t="n"/>
+      <c r="E12" s="38" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="22" t="inlineStr">
@@ -1050,6 +1130,10 @@
           <t>STEP 4: SPLT reports $224,789.09 as gross income on its 2025 1120.</t>
         </is>
       </c>
+      <c r="B13" s="37" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="38" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="21" t="inlineStr">
@@ -1057,6 +1141,10 @@
           <t>STEP 5 (belt-and-suspenders): Also request CORRECTED 1099-K from Amazon under SPLT TIN EIN 33-3094308.</t>
         </is>
       </c>
+      <c r="B14" s="37" t="n"/>
+      <c r="C14" s="37" t="n"/>
+      <c r="D14" s="37" t="n"/>
+      <c r="E14" s="38" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="22" t="inlineStr">
@@ -1064,6 +1152,10 @@
           <t>SPLIT DATE: Feb 4, 2025. Account moved to SPLT at SPLT formation Jan 28, 2025; effective order-date cutoff = Feb 4.</t>
         </is>
       </c>
+      <c r="B15" s="37" t="n"/>
+      <c r="C15" s="37" t="n"/>
+      <c r="D15" s="37" t="n"/>
+      <c r="E15" s="38" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="21" t="inlineStr">
@@ -1071,6 +1163,10 @@
           <t>BASIS: Order-date earned basis (NOT cash-landing). Amazon settlement lag means some Jan orders land in SPLT bank after Feb 4 — attribute by ORDER DATE.</t>
         </is>
       </c>
+      <c r="B16" s="37" t="n"/>
+      <c r="C16" s="37" t="n"/>
+      <c r="D16" s="37" t="n"/>
+      <c r="E16" s="38" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="23" t="inlineStr">
@@ -1078,6 +1174,10 @@
           <t>⚠️ FEES: Amazon fees on the $224,789.09 nominee portion FOLLOWED income to SPLT (~$53,030). SGM deducts fees only on its $15,220.80 slice ($7,071). See tab 5.</t>
         </is>
       </c>
+      <c r="B17" s="37" t="n"/>
+      <c r="C17" s="37" t="n"/>
+      <c r="D17" s="37" t="n"/>
+      <c r="E17" s="38" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -1581,7 +1681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1598,228 +1698,428 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Deduction Item</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Account</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Source / TJ Note</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Amazon platform fees (SGM slice, Jan 1–Feb 4)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>7071</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Settlement-sourced; fees follow income</t>
         </is>
       </c>
     </row>
     <row r="4" ht="56" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Amazon platform fees — SGM slice ($15,220.80 kept)</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>7071</v>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Augusta rule rent (warehouse $12,500 + home-office $4,000)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>16500</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>⚠️ TJ CONFIRM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>14-day cap; 4 Augusta payments = 4 days used; warehouse Jan–May only</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FB/Meta ads — SGM cards (···1400 $12,704 + ···0261 $2,736 + ···6559 $900)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>16340</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>SUBSTANTIATED</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>SGM WF …8625</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Amazon Seller Central settlement. SGM's slice only (~46.5% on pre-switch orders). Fees on nominee portion ($224,789) followed income to SPLT. Source: Layer 11.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="56" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Augusta rule rent — home office use</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="n">
-        <v>16500</v>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>⚠️ PENDING TJ</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>SGM WF …8625</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>Bank-substantiated (clean in SGM 2025 bank statements). Deductibility requires: (a) 14-day annual cap not exceeded; (b) no home-office double-stack. TJ confirms.</t>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Invoice-attributed; ···0261 debit in bank</t>
         </is>
       </c>
     </row>
     <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Facebook/Meta ads — SGM cards (···1400, ···0261, ···6559)</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>16340</v>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BANK_FEE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>732.77</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>SUBSTANTIATED</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>SGM cards</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>From 2025 FB invoice (134-txn, $97,769.11 total). SGM cards: ···1400 $12,704.23 + ···0261 $2,736.10 + ···6559 $900.00 = ~$16,340. ⚠️ ···0261 and ···6559 are bank debit cards — count from BANK (already in Layer 7 classification), NOT double-add from invoice.</t>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Bank service charges — SGM_2025_Txns</t>
         </is>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>Non-Amazon operating expenses (bank-classified — Layer 7)</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>34600</v>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>SGM WF …8625</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>Residual from Layer 7 bank classification. Total deductions needed = $74,511 to reach locked −$19,027 loss. Known items ($7,071 + $16,500 + $16,340 = $39,911) leave $34,600. TJ: itemize from ledger tab SGM_2025_Txns; verify each line traces to footed bank transaction.</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MEALS (gross — apply 50% haircut)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>610.75</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>⚠️ TJ — 50% rule</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>21 restaurant charges; TJ applies 50% → $305.38 deductible</t>
         </is>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Owner loans + AmEx personal charges — EXCLUDED</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>NON-DEDUCTIBLE</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>SGM→personal transfers = owner draw. Any personal AmEx payments charged to SGM bank = same treatment as SGM 2024 AmEx reclassification. Not business expenses.</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>OPEX_CONTRACTOR</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1881.35</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SGM_2025_Txns</t>
         </is>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>$148K SGM→SPLT operating transfer — EXCLUDED from P&amp;L</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>BALANCE SHEET</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>Interco cash movement (loan or capital — TJ decides). NOT an expense on SGM's P&amp;L.</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>OPEX_EDUCATION</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>259</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SGM_2025_Txns</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>TOTAL SUBSTANTIATED DEDUCTIONS</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="n">
-        <v>74511</v>
-      </c>
-      <c r="C10" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="19">
-        <f> $7,071 + $16,500 + $16,340 + $34,600. PROVISIONAL pending TJ itemization of $34,600 block and Augusta confirmation.</f>
-        <v/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>OPEX_INSURANCE (Next Insurance biz policy)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>93.67</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SGM_2025_Txns</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>OPEX_INSURANCE_VEHICLE (Tesla Insurance)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>820.05</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>⚠️ DROP — TJ confirm</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Standard mileage election bars vehicle insurance deduction</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="27" t="inlineStr">
-        <is>
-          <t>FILED-vs-BANK DEDUCTION CHECK (CB 2024 LESSON APPLIED)</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>OPEX_LEGAL_PATENT</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>670</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>USPTO fees; SGM_2025_Txns</t>
         </is>
       </c>
     </row>
     <row r="13" ht="130" customHeight="1">
-      <c r="A13" s="28" t="inlineStr">
-        <is>
-          <t>CB 2024 filed a commingled QuickBooks Self-Employed P&amp;L with ~$104K of unsubstantiated deductions. The same risk exists for SGM 2025.
-Math: Filed gross $130,976 − filed net (−$32,900) = implied filed expenses $163,876. This is a large expense load for a wind-down entity with only $55K of real revenue.
-⚠️ TJ ACTION: Provide the SGM 2025 1120-S filed deduction schedule (Part III / Schedule K). For each filed expense line:
-  (a) Trace to SGM WF …8625 bank transaction in Layer 7 footed classification.
-  (b) Flag any deduction with no bank/card source — unsubstantiated.
-  (c) Watch for personal costs, interco payments, or QB catch-all entries.
-Until TJ provides filed deduction detail, the filed-vs-amended deduction delta cannot be computed with precision. The amendment's own deductions are bank-substantiated.</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>OPEX_OTHER (net of flagged personal)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2362.35</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>⚠️ TJ REVIEW</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Includes $411 Westlake Baseball + $190 Reg Nursing (likely personal → ~$601 at risk); $800 CA FTX payment; T-Mobile biz %</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>OPEX_PLATFORM_FEE</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>154.75</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SGM_2025_Txns</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>OPEX_SHIPPING</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SGM_2025_Txns</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>OPEX_SOFTWARE</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>11044.71</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Veeqo, Klaviyo, Emotive, Shopify, Adobe; SGM_2025_Txns</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>OPEX_SUPPLIES</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2681.84</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SUBSTANTIATED</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SGM_2025_Txns</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>OPEX_TRAVEL (Airbnb Jan)</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1502.93</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>⚠️ TJ — biz purpose</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Airbnb 1/23 — Shark Tank prep period; document business purpose</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TRAVEL (Chicago trade show + Morocco)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4663.17</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>⚠️ TJ — biz purpose</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>$2,795 Int'l House Chicago + $961 Morocco (docs required); Air France $232.83 may be refunded — confirm credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SUBTOTAL — itemized opex (excl. rent)</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>27487.79</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Replaces $34,600 provisional</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Bank-sourced; TJ adjustments above reduce by est. $820–$1,421</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TOTAL DEDUCTIONS</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>67398.78999999999</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>FINAL (subject to TJ calls above)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Was $74,511 provisional</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NOTE: $34,600 PROVISIONAL block REPLACED — PROVISIONAL flag REMOVED. Opex now fully itemized from SGM_2025_Txns bank lines.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See SUBTOTAL row above; each line traces to footed SGM WF …8625 2025 statement</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A13:E13"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2402,11 +2702,11 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Non-Amazon opex (residual, Layer 7)</t>
+          <t>Non-Amazon opex (itemized from SGM_2025_Txns)</t>
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>34600</v>
+        <v>27487.79</v>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
@@ -2415,7 +2715,7 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>[PROVISIONAL] PROVISIONAL — residual deduction block. TJ to itemize from ledger tab; verify each line vs footed bank.</t>
+          <t>[CLEAN] Non-Amazon opex $27,487.79 — SUBSTANTIATED (itemized from SGM_2025_Txns; see 5_Deductions for line items). PROVISIONAL flag removed. V12-eligible.</t>
         </is>
       </c>
     </row>
@@ -2506,16 +2806,16 @@
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>-19027</v>
+        <v>-11915</v>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Computed: $55,484 gross − $74,511 deductions</t>
+          <t>Computed: $55,484 gross − $67,398.79 deductions</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>[PROVISIONAL] PROVISIONAL — pending TJ itemization of $34,600 opex block and Augusta confirmation. Favorable: loss deepens vs filed −$32,900. Does NOT raise tax.</t>
+          <t>[CLEAN] Amended net −$11,915 — FINAL (subject to TJ calls on vehicle insurance $820, meals 50%, travel biz-purpose docs). V12-eligible.</t>
         </is>
       </c>
     </row>
